--- a/etf_holdings/2026-10-08_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:00</t>
+          <t>2026-10-08 23:47:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,27 +509,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-2.93%1990</t>
+          <t>-1.26%1965</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.32%633,000</t>
+          <t>3.28%633,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>3.28%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:00</t>
+          <t>2026-10-08 23:47:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,27 +572,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0%2585</t>
+          <t>-1.35%2550</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.68%406,000</t>
+          <t>2.73%406,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:00</t>
+          <t>2026-10-08 23:47:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,27 +635,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.38%1305</t>
+          <t>-2.68%1270</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.23%667,000</t>
+          <t>2.27%667,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:01</t>
+          <t>2026-10-08 23:47:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.22%103,200</t>
+          <t>2.24%103,200</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.24%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:01</t>
+          <t>2026-10-08 23:47:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -756,27 +756,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.73%4835</t>
+          <t>+0.84%6000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.08%165,000</t>
+          <t>2.08%134,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -785,11 +785,11 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>165000</v>
+        <v>134000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:01</t>
+          <t>2026-10-08 23:47:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -819,40 +819,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.75%5950</t>
+          <t>-3%4690</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.05%134,000</t>
+          <t>2.08%165,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>134000</v>
+        <v>165000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:01</t>
+          <t>2026-10-08 23:47:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.90%418,400</t>
+          <t>1.91%418,400</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:01</t>
+          <t>2026-10-08 23:47:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.51%236,200</t>
+          <t>1.52%236,200</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:01</t>
+          <t>2026-10-08 23:47:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1008,40 +1008,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>6920LASERTEC CORP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.8%3545</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.49%158,000</t>
+          <t>1.52%62,100</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>158000</v>
+        <v>62100</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:01</t>
+          <t>2026-10-08 23:47:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,40 +1071,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6920LASERTEC CORP</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.96%3440</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.96%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.49%62,100</t>
+          <t>1.46%158,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>62100</v>
+        <v>158000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:02</t>
+          <t>2026-10-08 23:47:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.66%1480</t>
+          <t>-0.34%1475</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.66%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:02</t>
+          <t>2026-10-08 23:47:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,27 +1202,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.5%299.5</t>
+          <t>+1.67%304.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>299.5</t>
+          <t>304.5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.27%1,665,000</t>
+          <t>1.30%1,665,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:02</t>
+          <t>2026-10-08 23:47:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-1.71%2015</t>
+          <t>+2.73%2070</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-1.71%</t>
+          <t>+2.73%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:02</t>
+          <t>2026-10-08 23:47:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,27 +1328,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+2.13%2400</t>
+          <t>-2.92%2330</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+2.13%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.78%130,000</t>
+          <t>0.81%130,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:02</t>
+          <t>2026-10-08 23:47:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.73%7,234</t>
+          <t>0.72%7,234</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:02</t>
+          <t>2026-10-08 23:47:40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1454,27 +1454,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+3.66%595</t>
+          <t>-0.5%592</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+3.66%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>592</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.53%364,000</t>
+          <t>0.56%364,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">

--- a/etf_holdings/2026-10-08_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:38</t>
+          <t>2026-10-08 23:53:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:38</t>
+          <t>2026-10-08 23:53:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:38</t>
+          <t>2026-10-08 23:53:22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:39</t>
+          <t>2026-10-08 23:53:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:39</t>
+          <t>2026-10-08 23:53:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:39</t>
+          <t>2026-10-08 23:53:23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:39</t>
+          <t>2026-10-08 23:53:23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:39</t>
+          <t>2026-10-08 23:53:23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:39</t>
+          <t>2026-10-08 23:53:23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:39</t>
+          <t>2026-10-08 23:53:23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:40</t>
+          <t>2026-10-08 23:53:24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:40</t>
+          <t>2026-10-08 23:53:24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:40</t>
+          <t>2026-10-08 23:53:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:40</t>
+          <t>2026-10-08 23:53:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:40</t>
+          <t>2026-10-08 23:53:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 23:47:40</t>
+          <t>2026-10-08 23:53:24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
